--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
@@ -508,14 +508,10 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>21.7</v>
+        <v>17.2</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -531,9 +527,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -549,13 +551,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>37.2</v>
+        <v>35.2</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -571,14 +573,10 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -594,15 +592,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -617,15 +609,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -641,13 +627,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="E9" t="n">
         <v>15.5</v>
       </c>
       <c r="F9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -664,13 +650,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="E10" t="n">
         <v>17.4</v>
       </c>
       <c r="F10" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -686,15 +672,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -726,15 +706,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -766,9 +740,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -800,15 +780,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -823,9 +797,7 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>30.3</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -842,15 +814,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F19" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -865,15 +831,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F20" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -888,15 +848,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -911,9 +865,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>33</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.6</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -945,9 +905,15 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22.9</v>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -964,7 +930,9 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>32.9</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -983,10 +951,10 @@
         <v>30.4</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="F26" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1002,15 +970,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1048,15 +1010,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1072,13 +1028,13 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E30" t="n">
-        <v>16.3</v>
+        <v>14.7</v>
       </c>
       <c r="F30" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1098,10 +1054,10 @@
         <v>31.2</v>
       </c>
       <c r="E31" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="F31" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1117,15 +1073,9 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
@@ -508,10 +508,14 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="F3" t="n">
-        <v>17.2</v>
+        <v>21.6</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -528,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>33.8</v>
+        <v>34.8</v>
       </c>
       <c r="E4" t="n">
         <v>10.8</v>
       </c>
       <c r="F4" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -554,7 +558,7 @@
         <v>35.2</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
         <v>23.1</v>
@@ -573,10 +577,14 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.3</v>
+      </c>
       <c r="F6" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -627,13 +635,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="E9" t="n">
         <v>15.5</v>
       </c>
       <c r="F9" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -650,13 +658,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="E10" t="n">
         <v>17.4</v>
       </c>
       <c r="F10" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -689,9 +697,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -706,9 +720,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.9</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -740,15 +760,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -763,9 +777,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -780,9 +800,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24.7</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -797,9 +823,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -814,9 +846,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -831,9 +869,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23.9</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -848,9 +892,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.3</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -866,13 +916,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>33</v>
+        <v>33.8</v>
       </c>
       <c r="E22" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="F22" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -888,9 +938,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -906,13 +962,13 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>31.3</v>
+        <v>30.8</v>
       </c>
       <c r="E24" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="F24" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -928,10 +984,14 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17</v>
+      </c>
       <c r="F25" t="n">
-        <v>32.9</v>
+        <v>23.6</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -948,13 +1008,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>30.4</v>
+        <v>25.5</v>
       </c>
       <c r="E26" t="n">
-        <v>17.1</v>
+        <v>11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -970,9 +1030,15 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21.7</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -987,14 +1053,10 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>21.7</v>
+        <v>17.3</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1010,9 +1072,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23.8</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1028,13 +1096,13 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="E30" t="n">
-        <v>14.7</v>
+        <v>15.3</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1051,13 +1119,13 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="E31" t="n">
         <v>16.4</v>
       </c>
       <c r="F31" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1073,9 +1141,15 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.9</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
@@ -509,13 +509,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>32.9</v>
+        <v>31.8</v>
       </c>
       <c r="E3" t="n">
         <v>10.8</v>
       </c>
       <c r="F3" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>34.8</v>
+        <v>33.8</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F4" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -577,15 +577,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -634,15 +628,9 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -658,13 +646,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="E10" t="n">
         <v>17.4</v>
       </c>
       <c r="F10" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -680,9 +668,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23.3</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -697,15 +691,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>33</v>
-      </c>
-      <c r="E12" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -720,15 +708,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -760,9 +742,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -778,13 +766,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>34.8</v>
+        <v>31.8</v>
       </c>
       <c r="E16" t="n">
         <v>15.2</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -804,10 +792,10 @@
         <v>31.9</v>
       </c>
       <c r="E17" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F17" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -824,10 +812,10 @@
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="E18" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="F18" t="n">
         <v>22.6</v>
@@ -847,13 +835,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="E19" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="F19" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -870,13 +858,11 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>14.6</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>23.9</v>
+        <v>19.2</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -893,13 +879,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="E21" t="n">
-        <v>12.2</v>
+        <v>22.2</v>
       </c>
       <c r="F21" t="n">
-        <v>23.3</v>
+        <v>28.2</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -939,13 +925,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>30.8</v>
+        <v>31.3</v>
       </c>
       <c r="E23" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="F23" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -985,13 +971,13 @@
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="E25" t="n">
         <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1008,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="E26" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="F26" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1030,15 +1016,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1053,10 +1033,14 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>14.7</v>
+      </c>
       <c r="F28" t="n">
-        <v>17.3</v>
+        <v>22.7</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1073,7 +1057,7 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>31.4</v>
+        <v>31.41</v>
       </c>
       <c r="E29" t="n">
         <v>16.2</v>
@@ -1095,15 +1079,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1118,15 +1096,9 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F31" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1142,10 +1114,10 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E32" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
         <v>22.9</v>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_all_temperatures.xlsx
@@ -509,13 +509,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>31.8</v>
+        <v>32.9</v>
       </c>
       <c r="E3" t="n">
         <v>10.8</v>
       </c>
       <c r="F3" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -577,9 +577,15 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.7</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -594,9 +600,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.9</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -628,9 +640,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -646,13 +664,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E10" t="n">
         <v>17.4</v>
       </c>
       <c r="F10" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -668,15 +686,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -708,9 +720,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.9</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -742,15 +760,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>31</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -835,13 +847,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E19" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="F19" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -858,11 +870,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>33.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14.6</v>
+      </c>
       <c r="F20" t="n">
-        <v>19.2</v>
+        <v>23.9</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -879,13 +893,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="E21" t="n">
-        <v>22.2</v>
+        <v>12.2</v>
       </c>
       <c r="F21" t="n">
-        <v>28.2</v>
+        <v>23.3</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -905,7 +919,7 @@
         <v>33.8</v>
       </c>
       <c r="E22" t="n">
-        <v>10.6</v>
+        <v>20.6</v>
       </c>
       <c r="F22" t="n">
         <v>22.2</v>
@@ -925,13 +939,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E23" t="n">
         <v>14.6</v>
       </c>
       <c r="F23" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -994,7 +1008,7 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="E26" t="n">
         <v>11.9</v>
@@ -1057,7 +1071,7 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>31.41</v>
+        <v>31.4</v>
       </c>
       <c r="E29" t="n">
         <v>16.2</v>
@@ -1079,9 +1093,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23.2</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1096,9 +1116,15 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>23.3</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1114,10 +1140,10 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="E32" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="F32" t="n">
         <v>22.9</v>
